--- a/InputData/indst/_cement/BCtCR/BAU Clinker to Cement Ratio.xlsx
+++ b/InputData/indst/_cement/BCtCR/BAU Clinker to Cement Ratio.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\BCtCR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364B9E40-F7D3-4AED-ACEC-F9214AA7DF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530DC399-ECB4-4C89-ABBD-12D84FB0B4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Regions" sheetId="2" r:id="rId2"/>
     <sheet name="USGS MCS 2026 Cement" sheetId="3" r:id="rId3"/>
-    <sheet name="Derivation" sheetId="4" r:id="rId4"/>
-    <sheet name="BCtCR" sheetId="6" r:id="rId5"/>
+    <sheet name="US Product Mix" sheetId="7" r:id="rId4"/>
+    <sheet name="Derivation" sheetId="4" r:id="rId5"/>
+    <sheet name="BCtCR" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="163">
   <si>
     <t>BCtCR BAU Clinker to Cement Ratio</t>
   </si>
@@ -90,9 +91,6 @@
     <t>JUDGMENT</t>
   </si>
   <si>
-    <t>USGS-derived (see USGS tab); target = continued Type IL adoption</t>
-  </si>
-  <si>
     <t>China</t>
   </si>
   <si>
@@ -246,9 +244,6 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Blend ratio (rounded to 4 decimals)</t>
-  </si>
-  <si>
     <t>BAU Clinker to Cement Ratio</t>
   </si>
   <si>
@@ -393,35 +388,147 @@
     <t>Purpose and layout</t>
   </si>
   <si>
+    <t>Using it for other regions</t>
+  </si>
+  <si>
+    <t>We set this file up to be adaptable to each of the main EPS regions. If you are working on a non-US region, use the drop-down selector at the top of the 'Regions' tab to choose a different country. The Derivation then holds that country's starting ratio flat across 2021-2050, unless the Regions tab also gives a target ratio and target year, in which case the ratio moves in a straight line to the target and stays there. The 'BCtCR' tab updates on its own; just re-export the CSV. If your region is blank, or not listed, you will have to build the ratio on your own.</t>
+  </si>
+  <si>
+    <t>U.S. values</t>
+  </si>
+  <si>
+    <t>Other regions' values</t>
+  </si>
+  <si>
+    <t>Starting values for the other regions come from national cement associations, roadmaps, and press, listed under Sources. Each non-US value on the 'Regions' tab carries a tag showing how far to trust it: DIRECT means we read the number in the original document; SNIPPET means it came from a secondary summary, such as a trade-press article, and should be checked against the original; JUDGMENT means it is our own estimate or arithmetic, shown as a formula where possible. A blank means we have not found a good value yet. None of the non-US rows has a business-as-usual trend, so those ratios are held flat; the roadmap targets we found are policy goals and live in MACtCR instead. China is blank because the published figures conflict (roughly 0.66 against 0.74, with the China Cement Association disputing the rise), and Japan and Australia are blank because we have not found a value. The GCCA's GNR database holds regional detail but sits behind a login, so most values here come from association reports and trade press instead. Several rows are on a production basis rather than the consumption-blend basis used for the U.S.; that is close where net trade is small. The Mexico value is from 2016 and the EU value is for Europe in 2021, so both are due for updates.</t>
+  </si>
+  <si>
+    <t>Pick a region from the drop-down in B1. The Derivation and the export tab update on their own; re-export the CSV afterward. A blank cell means no sourced value yet.</t>
+  </si>
+  <si>
+    <t>TO FILL - conflicting snippets (0.657 vs 0.735, CCA disputes the rise); 53% utilization x 1.81 Bt capacity implies ~0.52, which also conflicts. Next: NBS clinker output + CCA annual report.</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>Blend ratio</t>
+  </si>
+  <si>
+    <t>U.S. business-as-usual clinker ratio from the cement product mix</t>
+  </si>
+  <si>
+    <t>USGS Mineral Industry Surveys, Cement (December issues): shipments including imports, million metric tons</t>
+  </si>
+  <si>
+    <t>Portland cement (ASTM C150)</t>
+  </si>
+  <si>
+    <t>Blended cement (ASTM C595)</t>
+  </si>
+  <si>
+    <t>Blended share of shipments</t>
+  </si>
+  <si>
+    <t>Type IL share of blended</t>
+  </si>
+  <si>
+    <t>Clinker content per metric ton of cement (PCA industry-average EPDs, 2019 data)</t>
+  </si>
+  <si>
+    <t>Portland cement, Type I/II</t>
+  </si>
+  <si>
+    <t>Type IL: clinker plus limestone (the rest is gypsum and minor additions)</t>
+  </si>
+  <si>
+    <t>Other blended cements (slag, pozzolan, ternary; EI estimate)</t>
+  </si>
+  <si>
+    <t>Business-as-usual assumptions at milestone years (EI judgment from the shipment trend; 2025 from data)</t>
+  </si>
+  <si>
+    <t>Other blended share of all cement</t>
+  </si>
+  <si>
+    <t>Limestone fraction of Type IL</t>
+  </si>
+  <si>
+    <t>Annual path (straight lines between milestone years)</t>
+  </si>
+  <si>
+    <t>Blended share</t>
+  </si>
+  <si>
+    <t>Other blended share</t>
+  </si>
+  <si>
+    <t>Type IL share of all cement</t>
+  </si>
+  <si>
+    <t>Portland (Type I/II) share</t>
+  </si>
+  <si>
+    <t>Unscaled clinker ratio</t>
+  </si>
+  <si>
+    <t>Clinker ratio (scaled to the 2025 USGS value)</t>
+  </si>
+  <si>
+    <t>Scale factor = 2025 USGS blend ratio / 2025 unscaled ratio (covers masonry cement, stock changes, and USGS estimation)</t>
+  </si>
+  <si>
+    <t>USGS MCS 2026 history; 2026-2050 from the 'US Product Mix' tab (product shares x PCA clinker contents)</t>
+  </si>
+  <si>
+    <t>U.S. cement product mix, 2019-2025</t>
+  </si>
+  <si>
+    <t>Mineral Industry Surveys: Cement (monthly; December issues 2019-2025 and May 2026)</t>
+  </si>
+  <si>
+    <t>https://www.usgs.gov/centers/national-minerals-information-center/cement-statistics-and-information</t>
+  </si>
+  <si>
+    <t>Shipments of portland cement (ASTM C150) and blended cement (ASTM C595), including imports, on the 'US Product Mix' tab. Blended cement rose from 2.4% of shipments in 2019 and 5.6% in 2021 to 24.2% (2022), 49.8% (2023), 59.5% (2024) and 64.6% (2025); about 96% of blended cement is Type IL. January-May 2026 was 63.1%, only 0.9 points above the same months of 2025, so the switch to Type IL has largely run its course. All 50 states had accepted Type IL by April 2024 (USGS Mineral Commodity Summaries 2025).</t>
+  </si>
+  <si>
+    <t>Clinker content of each cement type</t>
+  </si>
+  <si>
+    <t>Portland Cement Association (PCA)</t>
+  </si>
+  <si>
+    <t>Industry-average environmental product declarations for portland cement and portland-limestone cement (2019 data, revised July 2026)</t>
+  </si>
+  <si>
+    <t>https://www.cement.org/wp-content/uploads/2026/07/PCA_EPD_PLC_Athena_Final_revised_Jul2026.pdf</t>
+  </si>
+  <si>
+    <t>Type IL averages 82.7% clinker and 10.8% limestone; Type I/II averages 91.4% clinker. PCA's 2024 limestone cement report confirms the 10.8% average and the 15% limestone cap.</t>
+  </si>
+  <si>
+    <t>Official projections for comparison</t>
+  </si>
+  <si>
+    <t>U.S. Energy Information Administration</t>
+  </si>
+  <si>
+    <t>Industrial Demand Module of NEMS, AEO2025 documentation</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/outlooks/aeo/nems/documentation/industrial/pdf/IDM_AEO2025.pdf</t>
+  </si>
+  <si>
+    <t>AEO2025 holds cement additives constant (an implied clinker ratio of about 0.90), already above the recent data. DOE's Liftoff report (2023, updated 2025) uses a 0.89 baseline and treats 0.65 by the early 2030s as an aggressive scenario; PCA's roadmap aims for 0.85 by 2030, 0.80 by 2040 and 0.75 by 2050 as industry goals, not business as usual.</t>
+  </si>
+  <si>
     <t>This file gives the business-as-usual clinker-to-cement ratio: the metric tons of clinker in each metric ton of cement the region consumes. Clinker is the kiln product that causes nearly all of the cement industry's fuel use and process emissions, so this ratio is what turns cement demand (the BCD file) into clinker demand. It is a blend ratio: clinker used in the cement the region consumes, including clinker that is imported, divided by cement produced, with imported finished cement assumed to carry the same ratio. How much of that clinker is made inside the region is handled separately (BFoCDMbNI). In the policy case, the clinker-substitution lever lowers the ratio below this path, down toward the floor in MACtCR.
-The tabs run from inputs to output. 'Regions' holds the region selector and each region's starting ratio and optional target. 'USGS MCS 2026 Cement' holds the U.S. source data as published. 'Derivation' builds the 2021-2050 series, and the last tab, 'BCtCR', reads it directly. That 'BCtCR' tab is what gets exported to BCtCR.csv.</t>
-  </si>
-  <si>
-    <t>Using it for other regions</t>
-  </si>
-  <si>
-    <t>We set this file up to be adaptable to each of the main EPS regions. If you are working on a non-US region, use the drop-down selector at the top of the 'Regions' tab to choose a different country. The Derivation then holds that country's starting ratio flat across 2021-2050, unless the Regions tab also gives a target ratio and target year, in which case the ratio moves in a straight line to the target and stays there. The 'BCtCR' tab updates on its own; just re-export the CSV. If your region is blank, or not listed, you will have to build the ratio on your own.</t>
-  </si>
-  <si>
-    <t>U.S. values</t>
-  </si>
-  <si>
-    <t>For the U.S. national file version, we calculated the ratio for 2021-2025 (2025 estimated) from USGS production and import data, which gives 0.892, 0.883, 0.866, 0.855, and 0.829. The steady decline is the shift to portland-limestone (Type IL) cement. From 2026 the ratio falls in a straight line from 0.829 to 0.79 in 2035 and stays there. The 0.79 is our judgment about where the market-driven Type IL transition levels off. The Portland Cement Association's goal of 0.75 by 2050 is a roadmap target, not a business-as-usual projection, so it is not in this file; deeper reductions are the job of the clinker-substitution lever and the MACtCR floor.</t>
-  </si>
-  <si>
-    <t>Other regions' values</t>
-  </si>
-  <si>
-    <t>Starting values for the other regions come from national cement associations, roadmaps, and press, listed under Sources. Each non-US value on the 'Regions' tab carries a tag showing how far to trust it: DIRECT means we read the number in the original document; SNIPPET means it came from a secondary summary, such as a trade-press article, and should be checked against the original; JUDGMENT means it is our own estimate or arithmetic, shown as a formula where possible. A blank means we have not found a good value yet. None of the non-US rows has a business-as-usual trend, so those ratios are held flat; the roadmap targets we found are policy goals and live in MACtCR instead. China is blank because the published figures conflict (roughly 0.66 against 0.74, with the China Cement Association disputing the rise), and Japan and Australia are blank because we have not found a value. The GCCA's GNR database holds regional detail but sits behind a login, so most values here come from association reports and trade press instead. Several rows are on a production basis rather than the consumption-blend basis used for the U.S.; that is close where net trade is small. The Mexico value is from 2016 and the EU value is for Europe in 2021, so both are due for updates.</t>
-  </si>
-  <si>
-    <t>Pick a region from the drop-down in B1. The Derivation and the export tab update on their own; re-export the CSV afterward. A blank cell means no sourced value yet.</t>
-  </si>
-  <si>
-    <t>TO FILL - conflicting snippets (0.657 vs 0.735, CCA disputes the rise); 53% utilization x 1.81 Bt capacity implies ~0.52, which also conflicts. Next: NBS clinker output + CCA annual report.</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless</t>
+The tabs run from inputs to output. 'Regions' holds the region selector and each region's starting ratio and optional target. 'USGS MCS 2026 Cement' holds the U.S. production data as published. 'US Product Mix' projects the U.S. ratio from the mix of cement types and their clinker content. 'Derivation' builds the 2021-2050 series, and the last tab, 'BCtCR', reads it directly. That 'BCtCR' tab is what gets exported to BCtCR.csv.</t>
+  </si>
+  <si>
+    <t>For 2021-2025 (2025 estimated) the ratio comes from USGS production and import data: 0.892, 0.883, 0.866, 0.855 and 0.829. The decline is the shift to portland-limestone (Type IL) cement, which went from about 5% to 65% of shipments over those years.
+From 2026 the 'US Product Mix' tab projects the ratio from the share of each cement type times its clinker content (PCA's product declarations), scaled so 2025 matches USGS. That shift is now mostly complete, so the remaining business-as-usual decline is slow: a little more blended cement (68% of shipments by 2030, 72% by 2050), a little more slag and pozzolan cement (2.8% of all cement now, 5% by 2050), and Type IL limestone content drifting from 11% to 12.5% by 2035. The result is 0.820 in 2030, 0.813 in 2035, 0.811 in 2040 and 0.809 in 2050. The milestone shares are our judgment from the shipment trend; a reasonable range is 0.80-0.83 in 2035 and 0.79-0.83 in 2050. Deeper cuts are the job of the clinker-substitution lever and the MACtCR floor.</t>
   </si>
 </sst>
 </file>
@@ -499,7 +606,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -519,6 +626,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -824,306 +935,387 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="110.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="110.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="D5" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="10">
         <v>2026</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="B8" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+      <c r="D11" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
+      <c r="D12" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="10">
         <v>2023</v>
       </c>
-      <c r="D13" s="2">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B15" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="10">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B26" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="10"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B29" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B31" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B32" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D34" s="10">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+      <c r="D39" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+      <c r="D40" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D41" s="10">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+      <c r="D42" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B43" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
+      <c r="D43" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="10">
         <v>2026</v>
       </c>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+    </row>
+    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B50" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
-        <v>2026</v>
-      </c>
-      <c r="D27" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="2"/>
-      <c r="D34" s="2">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="8" t="s">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="B54" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="5" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="B55" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="2" t="s">
+    </row>
+    <row r="56" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="B56" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B57" s="10" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{971BA332-CEC4-490B-AC44-E9B2AEB1C463}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{E71A51AB-9AFE-411D-8E96-6D3EA343709D}"/>
-    <hyperlink ref="B21" r:id="rId3" xr:uid="{606CE6F9-6A43-4276-9F50-8B0188E7352E}"/>
-    <hyperlink ref="B28" r:id="rId4" xr:uid="{45397C74-1F46-4FC9-A7B0-62D76923C62C}"/>
-    <hyperlink ref="B35" r:id="rId5" xr:uid="{A6A285FA-A838-40C9-B5FC-4497907C4CF0}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{463E964B-6164-497F-AF25-DE1398683A72}"/>
-    <hyperlink ref="D14" r:id="rId7" xr:uid="{24257397-EECF-44A3-B013-18258C678D45}"/>
-    <hyperlink ref="D21" r:id="rId8" xr:uid="{30B20D4D-C276-4DAE-9325-997329773D9D}"/>
-    <hyperlink ref="D28" r:id="rId9" xr:uid="{3A8D0F01-E0D6-40D0-BFCA-5E19755B0D42}"/>
-    <hyperlink ref="D35" r:id="rId10" xr:uid="{0128DDBD-4CF7-4D10-A06D-0D8EBA49A36E}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{C700D560-08E7-4773-A6AD-C4F6EB1881D8}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{FE79DDC8-56CB-44E8-90CB-609A2174C5B3}"/>
+    <hyperlink ref="B21" r:id="rId3" xr:uid="{9C20D4DC-B105-48EB-8069-2BF89B91329A}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{5B8B1715-2EF4-4986-B66A-910AE5E320EE}"/>
+    <hyperlink ref="B35" r:id="rId5" xr:uid="{69D609EB-E3A6-4675-B74C-C167ACFB6E0C}"/>
+    <hyperlink ref="B42" r:id="rId6" xr:uid="{BB3E74BF-7C74-4E5B-8EC5-50B70C1DA8A5}"/>
+    <hyperlink ref="B49" r:id="rId7" xr:uid="{EE69548F-FDDD-42D8-90E5-DA63709DD7E8}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{E2A76FEA-C423-4807-A784-B258CC17768D}"/>
+    <hyperlink ref="D14" r:id="rId9" xr:uid="{8BFFD94F-83E9-452A-A252-2A80E15C71A1}"/>
+    <hyperlink ref="D21" r:id="rId10" xr:uid="{D33E374F-51A6-438D-A4E0-5FEC645047C9}"/>
+    <hyperlink ref="D28" r:id="rId11" xr:uid="{E9A40516-7A66-488D-8F96-BC8D68425EB7}"/>
+    <hyperlink ref="D35" r:id="rId12" xr:uid="{AA212CB0-DEE9-49FB-A501-F73A34940C64}"/>
+    <hyperlink ref="D42" r:id="rId13" xr:uid="{43BD38AB-CB14-4259-A71E-31B443FDA1F4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1132,7 +1324,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1144,7 +1336,7 @@
     <col min="8" max="8" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,12 +1344,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -1183,7 +1375,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1196,30 +1388,21 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="E5">
-        <v>0.79</v>
-      </c>
-      <c r="F5">
-        <v>2035</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
-      </c>
       <c r="H5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="H6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
       </c>
       <c r="B7">
         <v>2025</v>
@@ -1228,15 +1411,15 @@
         <v>0.73</v>
       </c>
       <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
         <v>20</v>
       </c>
-      <c r="H7" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
       </c>
       <c r="B8">
         <v>2021</v>
@@ -1248,20 +1431,20 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="H9" t="s">
         <v>24</v>
       </c>
-      <c r="H9" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
       </c>
       <c r="B10">
         <v>2022</v>
@@ -1273,12 +1456,12 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>28</v>
       </c>
       <c r="B11">
         <v>2016</v>
@@ -1290,12 +1473,12 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>30</v>
       </c>
       <c r="B12">
         <v>2020</v>
@@ -1307,33 +1490,33 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>32</v>
       </c>
       <c r="B13">
         <v>2025</v>
       </c>
       <c r="C13">
-        <f>ROUND((57.301-12.34)/63.912,2)</f>
-        <v>0.7</v>
+        <f>((57.301-12.34)/63.912)</f>
+        <v>0.70348291400675933</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
       <c r="H13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1349,19 +1532,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>36</v>
       </c>
       <c r="B3">
         <v>2021</v>
@@ -1376,12 +1559,12 @@
         <v>2024</v>
       </c>
       <c r="F3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>38</v>
       </c>
       <c r="B4">
         <v>91000</v>
@@ -1399,9 +1582,9 @@
         <v>84000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>79616</v>
@@ -1419,9 +1602,9 @@
         <v>69000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>108969</v>
@@ -1439,9 +1622,9 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>19937</v>
@@ -1459,9 +1642,9 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>1563</v>
@@ -1479,9 +1662,9 @@
         <v>660</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>939</v>
@@ -1499,9 +1682,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>111000</v>
@@ -1519,9 +1702,9 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>127</v>
@@ -1539,9 +1722,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>6280</v>
@@ -1559,9 +1742,9 @@
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>19</v>
@@ -1579,26 +1762,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
         <v>48</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>50</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>51</v>
       </c>
-      <c r="E15" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>53</v>
       </c>
       <c r="B16">
         <v>85000</v>
@@ -1613,9 +1796,9 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>65000</v>
@@ -1630,9 +1813,9 @@
         <v>61000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>1800000</v>
@@ -1647,9 +1830,9 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>53000</v>
@@ -1664,9 +1847,9 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>440000</v>
@@ -1681,9 +1864,9 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>68000</v>
@@ -1698,9 +1881,9 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22">
         <v>71000</v>
@@ -1715,9 +1898,9 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>46000</v>
@@ -1732,9 +1915,9 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>44000</v>
@@ -1749,9 +1932,9 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>44000</v>
@@ -1766,9 +1949,9 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>67000</v>
@@ -1783,9 +1966,9 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B27">
         <v>51000</v>
@@ -1800,9 +1983,9 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28">
         <v>85000</v>
@@ -1817,9 +2000,9 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29">
         <v>91000</v>
@@ -1834,9 +2017,9 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30">
         <v>860000</v>
@@ -1851,9 +2034,9 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31">
         <v>3900000</v>
@@ -1874,23 +2057,1144 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F556F18-732D-484F-A28B-9FC1C5B536EF}">
+  <dimension ref="A1:AA31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="62.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4">
+        <v>2019</v>
+      </c>
+      <c r="C4">
+        <v>2020</v>
+      </c>
+      <c r="D4">
+        <v>2021</v>
+      </c>
+      <c r="E4">
+        <v>2022</v>
+      </c>
+      <c r="F4">
+        <v>2023</v>
+      </c>
+      <c r="G4">
+        <v>2024</v>
+      </c>
+      <c r="H4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5">
+        <v>98.59</v>
+      </c>
+      <c r="C5">
+        <v>99.55</v>
+      </c>
+      <c r="D5">
+        <v>101.21</v>
+      </c>
+      <c r="E5">
+        <v>82.87</v>
+      </c>
+      <c r="F5">
+        <v>54.66</v>
+      </c>
+      <c r="G5">
+        <v>41.78</v>
+      </c>
+      <c r="H5">
+        <v>36.020000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="C6">
+        <v>3.28</v>
+      </c>
+      <c r="D6">
+        <v>6.04</v>
+      </c>
+      <c r="E6">
+        <v>26.39</v>
+      </c>
+      <c r="F6">
+        <v>54.21</v>
+      </c>
+      <c r="G6">
+        <v>61.41</v>
+      </c>
+      <c r="H6">
+        <v>65.599999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7">
+        <f t="shared" ref="B7:H7" si="0">B6/(B5+B6)</f>
+        <v>2.4054642645020788E-2</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>3.1897306233589419E-2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>5.631701631701632E-2</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0.24153395570199523</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0.49793331496279963</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0.59511580579513512</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>0.64554221609919293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="H8">
+        <v>0.95599999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11">
+        <v>0.91400000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12">
+        <v>0.93500000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16">
+        <v>2025</v>
+      </c>
+      <c r="C16">
+        <v>2030</v>
+      </c>
+      <c r="D16">
+        <v>2035</v>
+      </c>
+      <c r="E16">
+        <v>2040</v>
+      </c>
+      <c r="F16">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17">
+        <f>H7</f>
+        <v>0.64554221609919293</v>
+      </c>
+      <c r="C17">
+        <v>0.68</v>
+      </c>
+      <c r="D17">
+        <v>0.7</v>
+      </c>
+      <c r="E17">
+        <v>0.71</v>
+      </c>
+      <c r="F17">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18">
+        <f>H7*(1-H8)</f>
+        <v>2.8403857508364515E-2</v>
+      </c>
+      <c r="C18">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="D18">
+        <v>0.04</v>
+      </c>
+      <c r="E18">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="F18">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19">
+        <v>0.11</v>
+      </c>
+      <c r="C19">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="D19">
+        <v>0.125</v>
+      </c>
+      <c r="E19">
+        <v>0.125</v>
+      </c>
+      <c r="F19">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22">
+        <v>2025</v>
+      </c>
+      <c r="C22">
+        <v>2026</v>
+      </c>
+      <c r="D22">
+        <v>2027</v>
+      </c>
+      <c r="E22">
+        <v>2028</v>
+      </c>
+      <c r="F22">
+        <v>2029</v>
+      </c>
+      <c r="G22">
+        <v>2030</v>
+      </c>
+      <c r="H22">
+        <v>2031</v>
+      </c>
+      <c r="I22">
+        <v>2032</v>
+      </c>
+      <c r="J22">
+        <v>2033</v>
+      </c>
+      <c r="K22">
+        <v>2034</v>
+      </c>
+      <c r="L22">
+        <v>2035</v>
+      </c>
+      <c r="M22">
+        <v>2036</v>
+      </c>
+      <c r="N22">
+        <v>2037</v>
+      </c>
+      <c r="O22">
+        <v>2038</v>
+      </c>
+      <c r="P22">
+        <v>2039</v>
+      </c>
+      <c r="Q22">
+        <v>2040</v>
+      </c>
+      <c r="R22">
+        <v>2041</v>
+      </c>
+      <c r="S22">
+        <v>2042</v>
+      </c>
+      <c r="T22">
+        <v>2043</v>
+      </c>
+      <c r="U22">
+        <v>2044</v>
+      </c>
+      <c r="V22">
+        <v>2045</v>
+      </c>
+      <c r="W22">
+        <v>2046</v>
+      </c>
+      <c r="X22">
+        <v>2047</v>
+      </c>
+      <c r="Y22">
+        <v>2048</v>
+      </c>
+      <c r="Z22">
+        <v>2049</v>
+      </c>
+      <c r="AA22">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23">
+        <f t="shared" ref="B23:AA23" si="1">IF(B$22&lt;=2030,$B$17+($C$17-$B$17)*(B$22-2025)/5,IF(B$22&lt;=2035,$C$17+($D$17-$C$17)*(B$22-2030)/5,IF(B$22&lt;=2040,$D$17+($E$17-$D$17)*(B$22-2035)/5,$E$17+($F$17-$E$17)*(B$22-2040)/10)))</f>
+        <v>0.64554221609919293</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>0.65243377287935433</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>0.65932532965951574</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>0.66621688643967725</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>0.67310844321983865</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>0.68</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="1"/>
+        <v>0.68800000000000006</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="1"/>
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="1"/>
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="1"/>
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="1"/>
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="1"/>
+        <v>0.71</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="1"/>
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="1"/>
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="1"/>
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="1"/>
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="1"/>
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="1"/>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="X23">
+        <f t="shared" si="1"/>
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="1"/>
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="Z23">
+        <f t="shared" si="1"/>
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="AA23">
+        <f t="shared" si="1"/>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24">
+        <f t="shared" ref="B24:AA24" si="2">IF(B$22&lt;=2030,$B$18+($C$18-$B$18)*(B$22-2025)/5,IF(B$22&lt;=2035,$C$18+($D$18-$C$18)*(B$22-2030)/5,IF(B$22&lt;=2040,$D$18+($E$18-$D$18)*(B$22-2035)/5,$E$18+($F$18-$E$18)*(B$22-2040)/10)))</f>
+        <v>2.8403857508364515E-2</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="2"/>
+        <v>2.9523086006691613E-2</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="2"/>
+        <v>3.0642314505018711E-2</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="2"/>
+        <v>3.1761543003345806E-2</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>3.2880771501672908E-2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="2"/>
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="2"/>
+        <v>0.04</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="2"/>
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="2"/>
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="2"/>
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="2"/>
+        <v>4.24E-2</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="2"/>
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="2"/>
+        <v>4.3699999999999996E-2</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="2"/>
+        <v>4.4399999999999995E-2</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="2"/>
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="2"/>
+        <v>4.58E-2</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="2"/>
+        <v>4.65E-2</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="2"/>
+        <v>4.7199999999999999E-2</v>
+      </c>
+      <c r="X24">
+        <f t="shared" si="2"/>
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="2"/>
+        <v>4.8600000000000004E-2</v>
+      </c>
+      <c r="Z24">
+        <f t="shared" si="2"/>
+        <v>4.9300000000000004E-2</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ref="B25:AA25" si="3">B23-B24</f>
+        <v>0.61713835859082844</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="3"/>
+        <v>0.62291068687266271</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="3"/>
+        <v>0.62868301515449698</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="3"/>
+        <v>0.63445534343633148</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>0.64022767171816575</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="3"/>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="3"/>
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="3"/>
+        <v>0.65160000000000007</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>0.65439999999999998</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="3"/>
+        <v>0.65720000000000001</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="3"/>
+        <v>0.65999999999999992</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="3"/>
+        <v>0.66139999999999999</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="3"/>
+        <v>0.66279999999999994</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="3"/>
+        <v>0.66420000000000001</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="3"/>
+        <v>0.66559999999999997</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="3"/>
+        <v>0.66699999999999993</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="3"/>
+        <v>0.6673</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="3"/>
+        <v>0.66759999999999997</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="3"/>
+        <v>0.66789999999999994</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="3"/>
+        <v>0.66820000000000002</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="3"/>
+        <v>0.66849999999999998</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="3"/>
+        <v>0.66879999999999995</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="3"/>
+        <v>0.66910000000000003</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="3"/>
+        <v>0.6694</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" si="3"/>
+        <v>0.66969999999999996</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="3"/>
+        <v>0.66999999999999993</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26">
+        <f t="shared" ref="B26:AA26" si="4">1-B23</f>
+        <v>0.35445778390080707</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="4"/>
+        <v>0.34756622712064567</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="4"/>
+        <v>0.34067467034048426</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="4"/>
+        <v>0.33378311356032275</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="4"/>
+        <v>0.32689155678016135</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>0.31999999999999995</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="4"/>
+        <v>0.31599999999999995</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="4"/>
+        <v>0.31199999999999994</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="4"/>
+        <v>0.30800000000000005</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="4"/>
+        <v>0.30400000000000005</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="4"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="4"/>
+        <v>0.29800000000000004</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="4"/>
+        <v>0.29600000000000004</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="4"/>
+        <v>0.29400000000000004</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="4"/>
+        <v>0.29200000000000004</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="4"/>
+        <v>0.29000000000000004</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="4"/>
+        <v>0.28900000000000003</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="4"/>
+        <v>0.28800000000000003</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="4"/>
+        <v>0.28700000000000003</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="4"/>
+        <v>0.28600000000000003</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="4"/>
+        <v>0.28500000000000003</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="4"/>
+        <v>0.28400000000000003</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="4"/>
+        <v>0.28300000000000003</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="4"/>
+        <v>0.28200000000000003</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="4"/>
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="4"/>
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27">
+        <f t="shared" ref="B27:AA27" si="5">IF(B$22&lt;=2030,$B$19+($C$19-$B$19)*(B$22-2025)/5,IF(B$22&lt;=2035,$C$19+($D$19-$C$19)*(B$22-2030)/5,IF(B$22&lt;=2040,$D$19+($E$19-$D$19)*(B$22-2035)/5,$E$19+($F$19-$E$19)*(B$22-2040)/10)))</f>
+        <v>0.11</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="5"/>
+        <v>0.1116</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="5"/>
+        <v>0.1132</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="5"/>
+        <v>0.1148</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="5"/>
+        <v>0.11639999999999999</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="5"/>
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="5"/>
+        <v>0.11939999999999999</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="5"/>
+        <v>0.12079999999999999</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="5"/>
+        <v>0.1222</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="5"/>
+        <v>0.1236</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28">
+        <f t="shared" ref="B28:AA28" si="6">B26*$B$11+B25*($B$12-B27)+B24*$B$13</f>
+        <v>0.85157606770320804</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="6"/>
+        <v>0.84977019706357004</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="6"/>
+        <v>0.84794585497343045</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="6"/>
+        <v>0.8461030414327888</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="6"/>
+        <v>0.84424175644164545</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="6"/>
+        <v>0.84236200000000006</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="6"/>
+        <v>0.84086528000000005</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="6"/>
+        <v>0.83936072000000006</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="6"/>
+        <v>0.8378483200000002</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="6"/>
+        <v>0.83632808000000014</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="6"/>
+        <v>0.83479999999999999</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="6"/>
+        <v>0.83449600000000013</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="6"/>
+        <v>0.83419200000000004</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="6"/>
+        <v>0.83388800000000018</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="6"/>
+        <v>0.8335840000000001</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="6"/>
+        <v>0.83328000000000013</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="6"/>
+        <v>0.83306400000000003</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="6"/>
+        <v>0.83284800000000003</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="6"/>
+        <v>0.83263200000000004</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="6"/>
+        <v>0.83241599999999993</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="6"/>
+        <v>0.83220000000000005</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="6"/>
+        <v>0.83198400000000006</v>
+      </c>
+      <c r="X28">
+        <f t="shared" si="6"/>
+        <v>0.83176800000000017</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="6"/>
+        <v>0.83155200000000007</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="6"/>
+        <v>0.83133599999999996</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" si="6"/>
+        <v>0.83111999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29">
+        <f t="shared" ref="B29:AA29" si="7">B28*$B$31</f>
+        <v>0.82928571428571429</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="7"/>
+        <v>0.82752711305195847</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="7"/>
+        <v>0.8257505238655064</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="7"/>
+        <v>0.82395594672635764</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="7"/>
+        <v>0.82214338163451239</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="7"/>
+        <v>0.82031282858997057</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="7"/>
+        <v>0.81885528585085465</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="7"/>
+        <v>0.81739010832695957</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="7"/>
+        <v>0.81591729601828544</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="7"/>
+        <v>0.81443684892483192</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="7"/>
+        <v>0.81294876704659924</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="7"/>
+        <v>0.81265272437148894</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="7"/>
+        <v>0.81235668169637842</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="7"/>
+        <v>0.81206063902126813</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="7"/>
+        <v>0.81176459634615772</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="7"/>
+        <v>0.81146855367104731</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="7"/>
+        <v>0.81125820755978462</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="7"/>
+        <v>0.81104786144852192</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="7"/>
+        <v>0.81083751533725923</v>
+      </c>
+      <c r="U29">
+        <f t="shared" si="7"/>
+        <v>0.81062716922599654</v>
+      </c>
+      <c r="V29">
+        <f t="shared" si="7"/>
+        <v>0.81041682311473395</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="7"/>
+        <v>0.81020647700347126</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="7"/>
+        <v>0.80999613089220879</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="7"/>
+        <v>0.80978578478094598</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="7"/>
+        <v>0.80957543866968329</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="7"/>
+        <v>0.8093650925584206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31">
+        <f>Derivation!F10/B28</f>
+        <v>0.97382458917896408</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AE13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" t="str">
         <f>Regions!B1</f>
         <v>United States</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1899,7 +3203,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1908,41 +3212,41 @@
         <v>0.82930000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4">
         <f>IF(ISNUMBER(INDEX(Regions!$E$5:$E$14,MATCH(Regions!$B$1,Regions!$A$5:$A$14,0))),INDEX(Regions!$E$5:$E$14,MATCH(Regions!$B$1,Regions!$A$5:$A$14,0)),B3)</f>
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.82930000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5">
         <f>IF(ISNUMBER(INDEX(Regions!$F$5:$F$14,MATCH(Regions!$B$1,Regions!$A$5:$A$14,0))),INDEX(Regions!$F$5:$F$14,MATCH(Regions!$B$1,Regions!$A$5:$A$14,0)),B2)</f>
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6">
         <f>IF(B1="United States",1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>68</v>
       </c>
       <c r="B9">
         <v>2021</v>
@@ -1960,34 +3264,34 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="B10">
-        <f>ROUND(('USGS MCS 2026 Cement'!B5+'USGS MCS 2026 Cement'!B8)/'USGS MCS 2026 Cement'!B4,4)</f>
-        <v>0.8921</v>
+        <f>(('USGS MCS 2026 Cement'!B5+'USGS MCS 2026 Cement'!B8)/'USGS MCS 2026 Cement'!B4)</f>
+        <v>0.8920769230769231</v>
       </c>
       <c r="C10">
-        <f>ROUND(('USGS MCS 2026 Cement'!C5+'USGS MCS 2026 Cement'!C8)/'USGS MCS 2026 Cement'!C4,4)</f>
-        <v>0.88280000000000003</v>
+        <f>(('USGS MCS 2026 Cement'!C5+'USGS MCS 2026 Cement'!C8)/'USGS MCS 2026 Cement'!C4)</f>
+        <v>0.8827850877192982</v>
       </c>
       <c r="D10">
-        <f>ROUND(('USGS MCS 2026 Cement'!D5+'USGS MCS 2026 Cement'!D8)/'USGS MCS 2026 Cement'!D4,4)</f>
-        <v>0.86629999999999996</v>
+        <f>(('USGS MCS 2026 Cement'!D5+'USGS MCS 2026 Cement'!D8)/'USGS MCS 2026 Cement'!D4)</f>
+        <v>0.86633221850613151</v>
       </c>
       <c r="E10">
-        <f>ROUND(('USGS MCS 2026 Cement'!E5+'USGS MCS 2026 Cement'!E8)/'USGS MCS 2026 Cement'!E4,4)</f>
-        <v>0.85509999999999997</v>
+        <f>(('USGS MCS 2026 Cement'!E5+'USGS MCS 2026 Cement'!E8)/'USGS MCS 2026 Cement'!E4)</f>
+        <v>0.85511764705882354</v>
       </c>
       <c r="F10">
-        <f>ROUND(('USGS MCS 2026 Cement'!F5+'USGS MCS 2026 Cement'!F8)/'USGS MCS 2026 Cement'!F4,4)</f>
-        <v>0.82930000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+        <f>(('USGS MCS 2026 Cement'!F5+'USGS MCS 2026 Cement'!F8)/'USGS MCS 2026 Cement'!F4)</f>
+        <v>0.82928571428571429</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B12">
         <v>2021</v>
@@ -2080,129 +3384,129 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B13">
-        <f>IF(AND($B$6=1,B12&lt;=2025),B10,ROUND($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(B12-$B$2)/($B$5-$B$2)))),5))</f>
-        <v>0.8921</v>
+        <f>IF(AND($B$6=1,B12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(B12,'US Product Mix'!$B$22:$AA$22,0)),IF(AND($B$6=1,B12&lt;=2025),B10,($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(B12-$B$2)/($B$5-$B$2)))))))</f>
+        <v>0.8920769230769231</v>
       </c>
       <c r="C13">
-        <f>IF(AND($B$6=1,C12&lt;=2025),C10,ROUND($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(C12-$B$2)/($B$5-$B$2)))),5))</f>
-        <v>0.88280000000000003</v>
+        <f>IF(AND($B$6=1,C12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(C12,'US Product Mix'!$B$22:$AA$22,0)),IF(AND($B$6=1,C12&lt;=2025),C10,($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(C12-$B$2)/($B$5-$B$2)))))))</f>
+        <v>0.8827850877192982</v>
       </c>
       <c r="D13">
-        <f>IF(AND($B$6=1,D12&lt;=2025),D10,ROUND($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(D12-$B$2)/($B$5-$B$2)))),5))</f>
-        <v>0.86629999999999996</v>
+        <f>IF(AND($B$6=1,D12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(D12,'US Product Mix'!$B$22:$AA$22,0)),IF(AND($B$6=1,D12&lt;=2025),D10,($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(D12-$B$2)/($B$5-$B$2)))))))</f>
+        <v>0.86633221850613151</v>
       </c>
       <c r="E13">
-        <f>IF(AND($B$6=1,E12&lt;=2025),E10,ROUND($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(E12-$B$2)/($B$5-$B$2)))),5))</f>
-        <v>0.85509999999999997</v>
+        <f>IF(AND($B$6=1,E12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(E12,'US Product Mix'!$B$22:$AA$22,0)),IF(AND($B$6=1,E12&lt;=2025),E10,($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(E12-$B$2)/($B$5-$B$2)))))))</f>
+        <v>0.85511764705882354</v>
       </c>
       <c r="F13">
-        <f>IF(AND($B$6=1,F12&lt;=2025),F10,ROUND($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(F12-$B$2)/($B$5-$B$2)))),5))</f>
-        <v>0.82930000000000004</v>
+        <f>IF(AND($B$6=1,F12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(F12,'US Product Mix'!$B$22:$AA$22,0)),IF(AND($B$6=1,F12&lt;=2025),F10,($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(F12-$B$2)/($B$5-$B$2)))))))</f>
+        <v>0.82928571428571429</v>
       </c>
       <c r="G13">
-        <f t="shared" ref="G13:AE13" si="0">ROUND($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(G12-$B$2)/($B$5-$B$2)))),5)</f>
-        <v>0.82537000000000005</v>
+        <f>IF(AND($B$6=1,G12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(G12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(G12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.82752711305195847</v>
       </c>
       <c r="H13">
-        <f t="shared" si="0"/>
-        <v>0.82143999999999995</v>
+        <f>IF(AND($B$6=1,H12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(H12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(H12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.8257505238655064</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
-        <v>0.81750999999999996</v>
+        <f>IF(AND($B$6=1,I12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(I12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(I12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.82395594672635764</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
-        <v>0.81357999999999997</v>
+        <f>IF(AND($B$6=1,J12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(J12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(J12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.82214338163451239</v>
       </c>
       <c r="K13">
-        <f t="shared" si="0"/>
-        <v>0.80964999999999998</v>
+        <f>IF(AND($B$6=1,K12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(K12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(K12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.82031282858997057</v>
       </c>
       <c r="L13">
-        <f t="shared" si="0"/>
-        <v>0.80571999999999999</v>
+        <f>IF(AND($B$6=1,L12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(L12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(L12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81885528585085465</v>
       </c>
       <c r="M13">
-        <f t="shared" si="0"/>
-        <v>0.80179</v>
+        <f>IF(AND($B$6=1,M12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(M12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(M12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81739010832695957</v>
       </c>
       <c r="N13">
-        <f t="shared" si="0"/>
-        <v>0.79786000000000001</v>
+        <f>IF(AND($B$6=1,N12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(N12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(N12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81591729601828544</v>
       </c>
       <c r="O13">
-        <f t="shared" si="0"/>
-        <v>0.79393000000000002</v>
+        <f>IF(AND($B$6=1,O12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(O12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(O12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81443684892483192</v>
       </c>
       <c r="P13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,P12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(P12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(P12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81294876704659924</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,Q12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(Q12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(Q12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81265272437148894</v>
       </c>
       <c r="R13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,R12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(R12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(R12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81235668169637842</v>
       </c>
       <c r="S13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,S12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(S12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(S12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81206063902126813</v>
       </c>
       <c r="T13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,T12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(T12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(T12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81176459634615772</v>
       </c>
       <c r="U13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,U12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(U12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(U12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81146855367104731</v>
       </c>
       <c r="V13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,V12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(V12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(V12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81125820755978462</v>
       </c>
       <c r="W13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,W12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(W12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(W12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81104786144852192</v>
       </c>
       <c r="X13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,X12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(X12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(X12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81083751533725923</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,Y12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(Y12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(Y12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81062716922599654</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,Z12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(Z12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(Z12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81041682311473395</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,AA12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(AA12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(AA12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.81020647700347126</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,AB12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(AB12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(AB12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.80999613089220879</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,AC12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(AC12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(AC12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.80978578478094598</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,AD12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(AD12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(AD12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.80957543866968329</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="0"/>
-        <v>0.79</v>
+        <f>IF(AND($B$6=1,AE12&gt;2025),INDEX('US Product Mix'!$B$29:$AA$29,MATCH(AE12,'US Product Mix'!$B$22:$AA$22,0)),($B$3+($B$4-$B$3)*MAX(0,MIN(1,IF($B$5=$B$2,1,(AE12-$B$2)/($B$5-$B$2))))))</f>
+        <v>0.8093650925584206</v>
       </c>
     </row>
   </sheetData>
@@ -2210,17 +3514,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -2313,129 +3617,129 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B2">
         <f>Derivation!B13</f>
-        <v>0.8921</v>
+        <v>0.8920769230769231</v>
       </c>
       <c r="C2">
         <f>Derivation!C13</f>
-        <v>0.88280000000000003</v>
+        <v>0.8827850877192982</v>
       </c>
       <c r="D2">
         <f>Derivation!D13</f>
-        <v>0.86629999999999996</v>
+        <v>0.86633221850613151</v>
       </c>
       <c r="E2">
         <f>Derivation!E13</f>
-        <v>0.85509999999999997</v>
+        <v>0.85511764705882354</v>
       </c>
       <c r="F2">
         <f>Derivation!F13</f>
-        <v>0.82930000000000004</v>
+        <v>0.82928571428571429</v>
       </c>
       <c r="G2">
         <f>Derivation!G13</f>
-        <v>0.82537000000000005</v>
+        <v>0.82752711305195847</v>
       </c>
       <c r="H2">
         <f>Derivation!H13</f>
-        <v>0.82143999999999995</v>
+        <v>0.8257505238655064</v>
       </c>
       <c r="I2">
         <f>Derivation!I13</f>
-        <v>0.81750999999999996</v>
+        <v>0.82395594672635764</v>
       </c>
       <c r="J2">
         <f>Derivation!J13</f>
-        <v>0.81357999999999997</v>
+        <v>0.82214338163451239</v>
       </c>
       <c r="K2">
         <f>Derivation!K13</f>
-        <v>0.80964999999999998</v>
+        <v>0.82031282858997057</v>
       </c>
       <c r="L2">
         <f>Derivation!L13</f>
-        <v>0.80571999999999999</v>
+        <v>0.81885528585085465</v>
       </c>
       <c r="M2">
         <f>Derivation!M13</f>
-        <v>0.80179</v>
+        <v>0.81739010832695957</v>
       </c>
       <c r="N2">
         <f>Derivation!N13</f>
-        <v>0.79786000000000001</v>
+        <v>0.81591729601828544</v>
       </c>
       <c r="O2">
         <f>Derivation!O13</f>
-        <v>0.79393000000000002</v>
+        <v>0.81443684892483192</v>
       </c>
       <c r="P2">
         <f>Derivation!P13</f>
-        <v>0.79</v>
+        <v>0.81294876704659924</v>
       </c>
       <c r="Q2">
         <f>Derivation!Q13</f>
-        <v>0.79</v>
+        <v>0.81265272437148894</v>
       </c>
       <c r="R2">
         <f>Derivation!R13</f>
-        <v>0.79</v>
+        <v>0.81235668169637842</v>
       </c>
       <c r="S2">
         <f>Derivation!S13</f>
-        <v>0.79</v>
+        <v>0.81206063902126813</v>
       </c>
       <c r="T2">
         <f>Derivation!T13</f>
-        <v>0.79</v>
+        <v>0.81176459634615772</v>
       </c>
       <c r="U2">
         <f>Derivation!U13</f>
-        <v>0.79</v>
+        <v>0.81146855367104731</v>
       </c>
       <c r="V2">
         <f>Derivation!V13</f>
-        <v>0.79</v>
+        <v>0.81125820755978462</v>
       </c>
       <c r="W2">
         <f>Derivation!W13</f>
-        <v>0.79</v>
+        <v>0.81104786144852192</v>
       </c>
       <c r="X2">
         <f>Derivation!X13</f>
-        <v>0.79</v>
+        <v>0.81083751533725923</v>
       </c>
       <c r="Y2">
         <f>Derivation!Y13</f>
-        <v>0.79</v>
+        <v>0.81062716922599654</v>
       </c>
       <c r="Z2">
         <f>Derivation!Z13</f>
-        <v>0.79</v>
+        <v>0.81041682311473395</v>
       </c>
       <c r="AA2">
         <f>Derivation!AA13</f>
-        <v>0.79</v>
+        <v>0.81020647700347126</v>
       </c>
       <c r="AB2">
         <f>Derivation!AB13</f>
-        <v>0.79</v>
+        <v>0.80999613089220879</v>
       </c>
       <c r="AC2">
         <f>Derivation!AC13</f>
-        <v>0.79</v>
+        <v>0.80978578478094598</v>
       </c>
       <c r="AD2">
         <f>Derivation!AD13</f>
-        <v>0.79</v>
+        <v>0.80957543866968329</v>
       </c>
       <c r="AE2">
         <f>Derivation!AE13</f>
-        <v>0.79</v>
+        <v>0.8093650925584206</v>
       </c>
     </row>
   </sheetData>
